--- a/data/activities.xlsx
+++ b/data/activities.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gautam-research.github.io\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vipin\New Volume\gautam-research.github.io\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F90C379E-17C6-4DB8-8E13-FC7B036D2077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96513018-7F25-4DBE-A548-8D6AB5D5FA3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,28 +25,144 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
-  <si>
-    <t>Title</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Image</t>
-  </si>
-  <si>
-    <t>Link</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="40">
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>image</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>link</t>
+  </si>
+  <si>
+    <t>button</t>
+  </si>
+  <si>
+    <t>ETAAV - 2025, IISC Bangalore</t>
+  </si>
+  <si>
+    <t>images/ETAAV.png</t>
+  </si>
+  <si>
+    <t>https://sites.google.com/view/etaav2025</t>
+  </si>
+  <si>
+    <t>Learn More</t>
+  </si>
+  <si>
+    <t>I had the privilege of presenting our research at ETAAV 2025, hosted by IISc Bangalore. Our work included RGB-IR Object Detection in Aerial Imagery via Spectral-Aware Augmentation Techniques and UAV-Based Aerial Object Imagery for Animal Ecology. We were also proud to secure 1st Place in the UAV EO-IR Slant Angle Object Detection Challenge on Kaggle.</t>
+  </si>
+  <si>
+    <t>IInvenTiv - 2025, IIT Madras</t>
+  </si>
+  <si>
+    <t>images/img1.jpeg</t>
+  </si>
+  <si>
+    <t>IInvenTiv is a mega R&amp;D fair where top institutions showcase their research and development. Proud to represent our institute and present research work on helmet detection in aerial views.</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/posts/indian-institute-of-technology-iit-goa_the-3rd-edition-of-iinventive-an-rd-innovation-activity-7301209027122708482-ox6a</t>
+  </si>
+  <si>
+    <t>CVIP 2024 IIITM Kancheepuram</t>
+  </si>
+  <si>
+    <t>images/img2.JPG</t>
+  </si>
+  <si>
+    <t>Presented 3 Research Papers at CVIP 2024, IIITM Kancheepuram. Best Paper Award – SkyGuard: Semi-Supervised Drone Technology for Real-time Traffic Rule Enforcement.</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/posts/indian-institute-of-technology-iit-goa_iitgoa-researchexcellence-computervision-activity-7276981386874413056-K43E</t>
+  </si>
+  <si>
+    <t>Peek</t>
+  </si>
+  <si>
+    <t>CVIP 2023, IIT Jammu</t>
+  </si>
+  <si>
+    <t>images/img3.jpg</t>
+  </si>
+  <si>
+    <t>At CVIP 2023 IIT Jammu, with Prof. Venkatesh Kamat and Prof. Shitala Prasad.</t>
+  </si>
+  <si>
+    <t>Vibrant Goa Tech Summit 2024</t>
+  </si>
+  <si>
+    <t>images/img4.jpg</t>
+  </si>
+  <si>
+    <t>Represented our institute over 3 days and received a special recognition award for research in drone technology.</t>
+  </si>
+  <si>
+    <t>https://iitgoa.ac.in/event-detail/?id=265</t>
+  </si>
+  <si>
+    <t>Guest Lecture at Padre Conceição College Of Engineering</t>
+  </si>
+  <si>
+    <t>images/img5.jpg</t>
+  </si>
+  <si>
+    <t>Conducted a seminar on TinyML for Healthcare and Deployment Challenges on Low-Power Edge Computing Boards.</t>
+  </si>
+  <si>
+    <t>https://pccegoa.edu.in/2024/07/19/the-ace-student-chapter-installation-ceremony-2024-25/</t>
+  </si>
+  <si>
+    <t>Workshop arranged by Center for Drone Applications</t>
+  </si>
+  <si>
+    <t>images/img6.JPG</t>
+  </si>
+  <si>
+    <t>Hosted a national-level workshop with 100+ participants and delivered sessions on Drones and Applications and Fundamentals of Drone Systems.</t>
+  </si>
+  <si>
+    <t>M.Tech Graduation – Computer Science &amp; Engineering</t>
+  </si>
+  <si>
+    <t>images/graduation.jpg</t>
+  </si>
+  <si>
+    <t>Successfully graduated with an M.Tech degree in Computer Science and Engineering with an A+ grade in thesis.</t>
+  </si>
+  <si>
+    <t>LPCVC 2026 – CVPR 2026, Denver</t>
+  </si>
+  <si>
+    <t>https://lpcv.ai/2026LPCVC/winners/</t>
+  </si>
+  <si>
+    <t>Proud to share that our team &lt;strong&gt;CDA-IITGoa&lt;/strong&gt; secured &lt;strong&gt;3rd Place in Track-2&lt;/strong&gt; at the IEEE Low-Power Computer Vision Challenge (LPCVC) 2026, organized as part of the &lt;strong&gt;Efficient Deep Learning for Computer Vision (ECV) Workshop&lt;/strong&gt; at &lt;strong&gt;CVPR 2026, Denver&lt;/strong&gt;. Track-2 focused on &lt;em&gt;Action Recognition in Video&lt;/em&gt;, and this achievement reflects our efforts toward building efficient and robust video understanding solutions for low-power edge devices.</t>
+  </si>
+  <si>
+    <t>images/lpcvc.png</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -69,13 +185,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -354,10 +476,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -370,8 +499,149 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{4EE8DFDD-9142-4067-8760-DA514A55D7CB}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>